--- a/Experiments data/Contraction Limit/Contraction_Limit_PGP_Graph.xlsx
+++ b/Experiments data/Contraction Limit/Contraction_Limit_PGP_Graph.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\SISR Script\Experiments data\Contraction Limit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Contraction Limit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBE90CF4-8BA9-410C-B6BC-7E0DBA3E230F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED8CB9B-757D-4700-9CD7-8B7B2CEE9B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="38">
   <si>
     <t>KaHIP</t>
   </si>
@@ -124,6 +124,36 @@
   <si>
     <t>Deep Multilevel, ε= 0</t>
   </si>
+  <si>
+    <t>K = 4, Graph = PGP, Contraction = 70%, Cardinality Sizes = [1726, 2244, 2917, 3793] at f = 0.3, CL= 1602</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 200</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 400</t>
+  </si>
+  <si>
+    <t>Deep Multilevel, ε = 800</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε= 0</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 200</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 400</t>
+  </si>
+  <si>
+    <t>Deep NUGP, ε = 800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edge Cut </t>
+  </si>
+  <si>
+    <t>Deep NUGP</t>
+  </si>
 </sst>
 </file>
 
@@ -194,7 +224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -276,12 +306,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -309,6 +350,10 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -330,8 +375,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -682,7 +733,7 @@
                   <c:v>2268.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2006.6</c:v>
+                  <c:v>825.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -703,7 +754,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 0.05</c:v>
+                  <c:v>Deep Multilevel, ε = 200</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -775,7 +826,7 @@
                   <c:v>1281.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1117.5999999999999</c:v>
+                  <c:v>808.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1457,13 +1508,27 @@
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
+                  <a:sysClr val="windowText" lastClr="000000">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  </a:sysClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1471,16 +1536,14 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
-                </a:solidFill>
+              <a:rPr lang="en-US" sz="1800" b="0" i="0" baseline="0">
+                <a:effectLst/>
               </a:rPr>
-              <a:t>Edge Cut as Contraction Limit Increases</a:t>
+              <a:t>Edge Cut as Epislon Increases</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US" sz="1600">
+              <a:effectLst/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1496,13 +1559,27 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
+                <a:sysClr val="windowText" lastClr="000000">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
-                </a:schemeClr>
+                </a:sysClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1516,8 +1593,9 @@
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -1534,162 +1612,100 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>'Edge Cuts'!$I$65:$I$68</c:f>
+              <c:f>'Edge Cuts'!$I$68</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Edge Cuts'!$J$65:$J$68</c:f>
+              <c:f>'Edge Cuts'!$J$68</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.4186260949746427</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.43337943752881519</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.4021822652528047</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>0.41509143998770553</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-FFF1-4933-A1F2-02FE4A2A580F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Edge Cuts'!$K$64</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>KaHIP</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Edge Cuts'!$I$65:$I$68</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.7</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Edge Cuts'!$K$65:$K$68</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FFF1-4933-A1F2-02FE4A2A580F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1702,78 +1718,103 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε= 0</c:v>
+                  <c:v>Deep NUGP, ε= 0</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>'Edge Cuts'!$I$65:$I$68</c:f>
+              <c:f>'Edge Cuts'!$I$68</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Edge Cuts'!$L$65:$L$68</c:f>
+              <c:f>'Edge Cuts'!$L$68</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>-1.0444137083141229</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.56277854618103562</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>-0.74304595051483013</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>-0.54187797756262468</c:v>
+                  <c:v>0.36575995082219154</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-FFF1-4933-A1F2-02FE4A2A580F}"/>
@@ -1789,97 +1830,516 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Deep Multilevel, ε = 5</c:v>
+                  <c:v>Deep NUGP, ε = 200</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
             <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
               <a:effectLst/>
             </c:spPr>
-          </c:marker>
-          <c:xVal>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
             <c:numRef>
-              <c:f>'Edge Cuts'!$I$65:$I$68</c:f>
+              <c:f>'Edge Cuts'!$I$68</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>0.15</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.35</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.55000000000000004</c:v>
-                </c:pt>
-                <c:pt idx="3">
                   <c:v>0.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:xVal>
-          <c:yVal>
+          </c:cat>
+          <c:val>
             <c:numRef>
-              <c:f>'Edge Cuts'!$M$65:$M$68</c:f>
+              <c:f>'Edge Cuts'!$M$68</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>-3.3348701398493823E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>-0.34332257568772084</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1.5521745812202278E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.14123251882587995</c:v>
+                  <c:v>0.37866912555709237</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:yVal>
-          <c:smooth val="1"/>
+          </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-FFF1-4933-A1F2-02FE4A2A580F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Edge Cuts'!$N$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP, ε = 400</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent5"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$I$68</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$N$68</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.40018441678192718</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-06BC-4930-A91C-1F7912EEDFE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Edge Cuts'!$O$64</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP, ε = 800</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$I$68</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$O$68</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.46334716459197794</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-06BC-4930-A91C-1F7912EEDFE3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:gapWidth val="150"/>
         <c:axId val="130200223"/>
         <c:axId val="1092910383"/>
-      </c:scatterChart>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Edge Cuts'!$K$64</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>KaHIP</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="en-US"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="outEnd"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Edge Cuts'!$I$68</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0%</c:formatCode>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>0.7</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'Edge Cuts'!$K$68</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>0%</c:formatCode>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>0</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-FFF1-4933-A1F2-02FE4A2A580F}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="130200223"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1092910383"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
       <c:valAx>
-        <c:axId val="130200223"/>
+        <c:axId val="1092910383"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1906,7 +2366,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1919,131 +2379,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:sysClr val="windowText" lastClr="000000">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:sysClr>
-                    </a:solidFill>
-                  </a:rPr>
-                  <a:t>Precentage of Contraction Limit</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1092910383"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1092910383"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000">
                         <a:lumMod val="65000"/>
@@ -2066,11 +2402,11 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
                       <a:lumMod val="65000"/>
@@ -2125,7 +2461,7 @@
         </c:txPr>
         <c:crossAx val="130200223"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
+        <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -2150,7 +2486,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -2211,6 +2547,1313 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Observing Edge cut as Epislon varies (PGP graph)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Edge Cuts'!$D$104</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:delete val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-5.4636590946577974E-2"/>
+                  <c:y val="-4.2622614372255507E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{047ED373-BC25-4CFB-8D99-47DB7B82F861}" type="YVALUE">
+                      <a:rPr lang="en-US" sz="1200"/>
+                      <a:pPr/>
+                      <a:t>[Y VALUE]</a:t>
+                    </a:fld>
+                    <a:r>
+                      <a:rPr lang="en-US" sz="1200"/>
+                      <a:t> / Unfeasible</a:t>
+                    </a:r>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="0"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-4EBD-4154-A4C2-00C35791FB95}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$C$105:$C$114</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>382</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>573</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>764</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>955</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1146</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1337</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1528</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1719</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$D$105:$D$114</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>917</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>873</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>812</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>736</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>697</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>731</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>766</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1090</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1428</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4EBD-4154-A4C2-00C35791FB95}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="243241631"/>
+        <c:axId val="243243551"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="243241631"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Epislon Values (Upper Bound = min(Partition size) - 1)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.1818480386764415"/>
+              <c:y val="0.89295955013692752"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="243243551"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="191"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="243243551"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Edge Cut Values (lower is better)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.8537791550562191E-2"/>
+              <c:y val="0.13418812690048385"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="243241631"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="windowText" lastClr="000000">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:sysClr>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>Observing CCM as Epislon Varies (PGP Graph)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Edge Cuts'!$G$104</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Deep NUGP</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$F$105:$F$114</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>382</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>573</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>764</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>955</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1146</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1337</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1528</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1719</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Edge Cuts'!$G$105:$G$114</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.5799999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.15355805243445E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.12191011235955</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.143071161048689</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.21142322097378199</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.42621722846441901</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.38876404494382</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.41217228464419398</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.45850000000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3BD8-4150-AFF5-3C5983602961}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1156126143"/>
+        <c:axId val="1156127103"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1156126143"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>Epislon Values (Upper Bound = min(Partition size) - 1)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1156127103"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+        <c:majorUnit val="191"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1156127103"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:sysClr>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>CCM Values </a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1156126143"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -2540,7 +4183,7 @@
                   <c:v>2.5937999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.2334000000000005</c:v>
+                  <c:v>3.4652000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3410,7 +5053,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4114,7 +5757,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -4815,7 +6458,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5147,7 +6790,7 @@
                   <c:v>950.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>832.4</c:v>
+                  <c:v>129.80000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6197,6 +7840,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -8778,6 +10501,1038 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -9334,15 +12089,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>790013</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>45942</xdr:rowOff>
+      <xdr:colOff>610719</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>124383</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>470647</xdr:colOff>
-      <xdr:row>96</xdr:row>
-      <xdr:rowOff>56029</xdr:rowOff>
+      <xdr:colOff>291353</xdr:colOff>
+      <xdr:row>101</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -9362,6 +12117,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>778807</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>101971</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>291352</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>179292</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{474ABBA1-52F0-6F61-97E1-BB58FBAAD1F7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>605116</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>113178</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>291351</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EE49C95-DE34-BAB4-5135-689DFAB474E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -9587,86 +12414,89 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
-        <row r="65">
-          <cell r="E65" t="str">
-            <v>KaMinPar</v>
-          </cell>
-          <cell r="F65" t="str">
-            <v>KaHIP</v>
-          </cell>
-          <cell r="G65" t="str">
-            <v>Deep Multilevel, ε= 0</v>
-          </cell>
-          <cell r="H65" t="str">
-            <v>Deep Multilevel, ε = 5</v>
+        <row r="102">
+          <cell r="B102" t="str">
+            <v>Deep NUGP</v>
           </cell>
         </row>
-        <row r="66">
-          <cell r="D66">
-            <v>0.15</v>
-          </cell>
-          <cell r="E66">
-            <v>-5.0253573075149729E-2</v>
-          </cell>
-          <cell r="F66">
+        <row r="103">
+          <cell r="A103">
             <v>0</v>
           </cell>
-          <cell r="G66">
-            <v>-0.29322268326417694</v>
-          </cell>
-          <cell r="H66">
-            <v>-0.2259105578607653</v>
+          <cell r="B103">
+            <v>1318</v>
           </cell>
         </row>
-        <row r="67">
-          <cell r="D67">
-            <v>0.35</v>
+        <row r="104">
+          <cell r="A104">
+            <v>20</v>
           </cell>
-          <cell r="E67">
-            <v>-0.11234055632395866</v>
-          </cell>
-          <cell r="F67">
-            <v>0</v>
-          </cell>
-          <cell r="G67">
-            <v>-8.0528661441524471E-2</v>
-          </cell>
-          <cell r="H67">
-            <v>-0.16612878438604564</v>
+          <cell r="B104">
+            <v>1319</v>
           </cell>
         </row>
-        <row r="68">
-          <cell r="D68">
-            <v>0.55000000000000004</v>
+        <row r="105">
+          <cell r="A105">
+            <v>40</v>
           </cell>
-          <cell r="E68">
-            <v>-0.12156139542031644</v>
-          </cell>
-          <cell r="F68">
-            <v>0</v>
-          </cell>
-          <cell r="G68">
-            <v>-0.17273705240510215</v>
-          </cell>
-          <cell r="H68">
-            <v>-0.18579990779160899</v>
+          <cell r="B105">
+            <v>1307</v>
           </cell>
         </row>
-        <row r="69">
-          <cell r="D69">
-            <v>0.7</v>
+        <row r="106">
+          <cell r="A106">
+            <v>60</v>
           </cell>
-          <cell r="E69">
-            <v>-0.11065006915629322</v>
+          <cell r="B106">
+            <v>1258</v>
           </cell>
-          <cell r="F69">
-            <v>0</v>
+        </row>
+        <row r="107">
+          <cell r="A107">
+            <v>80</v>
           </cell>
-          <cell r="G69">
-            <v>-0.2365145228215767</v>
+          <cell r="B107">
+            <v>1159</v>
           </cell>
-          <cell r="H69">
-            <v>-0.19087136929460569</v>
+        </row>
+        <row r="108">
+          <cell r="A108">
+            <v>100</v>
+          </cell>
+          <cell r="B108">
+            <v>1149</v>
+          </cell>
+        </row>
+        <row r="109">
+          <cell r="A109">
+            <v>120</v>
+          </cell>
+          <cell r="B109">
+            <v>1234</v>
+          </cell>
+        </row>
+        <row r="110">
+          <cell r="A110">
+            <v>140</v>
+          </cell>
+          <cell r="B110">
+            <v>1341</v>
+          </cell>
+        </row>
+        <row r="111">
+          <cell r="A111">
+            <v>160</v>
+          </cell>
+          <cell r="B111">
+            <v>1416</v>
+          </cell>
+        </row>
+        <row r="112">
+          <cell r="A112">
+            <v>180</v>
+          </cell>
+          <cell r="B112">
+            <v>1659</v>
           </cell>
         </row>
       </sheetData>
@@ -9965,7 +12795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M68"/>
+  <dimension ref="A1:O114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -9975,6 +12805,7 @@
     <col min="5" max="5" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -9986,26 +12817,26 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
@@ -10185,26 +13016,26 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
@@ -10384,26 +13215,26 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+      <c r="A28" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
+      <c r="B29" s="17"/>
+      <c r="C29" s="17"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
@@ -10490,7 +13321,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>12</v>
       </c>
@@ -10519,7 +13350,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>13</v>
       </c>
@@ -10548,7 +13379,7 @@
         <v>1564</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>14</v>
       </c>
@@ -10577,34 +13408,34 @@
         <v>955</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C40" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" s="16"/>
+      <c r="C41" s="16"/>
+      <c r="D41" s="16"/>
+      <c r="E41" s="16"/>
+      <c r="F41" s="16"/>
+      <c r="G41" s="16"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-    </row>
-    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+    </row>
+    <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="1" t="s">
         <v>6</v>
@@ -10628,10 +13459,16 @@
         <v>24</v>
       </c>
       <c r="I43" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="J43" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>10</v>
       </c>
@@ -10654,13 +13491,19 @@
         <v>1271</v>
       </c>
       <c r="H44">
-        <v>1755</v>
+        <v>821</v>
       </c>
       <c r="I44">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+        <v>780</v>
+      </c>
+      <c r="J44">
+        <v>804</v>
+      </c>
+      <c r="K44">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>11</v>
       </c>
@@ -10683,13 +13526,19 @@
         <v>1376</v>
       </c>
       <c r="H45">
-        <v>2369</v>
+        <v>932</v>
       </c>
       <c r="I45">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+      <c r="J45">
+        <v>731</v>
+      </c>
+      <c r="K45">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>12</v>
       </c>
@@ -10712,13 +13561,19 @@
         <v>1302</v>
       </c>
       <c r="H46">
-        <v>1977</v>
+        <v>869</v>
       </c>
       <c r="I46">
-        <v>1481</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+        <v>801</v>
+      </c>
+      <c r="J46">
+        <v>854</v>
+      </c>
+      <c r="K46">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>13</v>
       </c>
@@ -10741,13 +13596,19 @@
         <v>1273</v>
       </c>
       <c r="H47">
-        <v>1624</v>
+        <v>803</v>
       </c>
       <c r="I47">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+        <v>766</v>
+      </c>
+      <c r="J47">
+        <v>711</v>
+      </c>
+      <c r="K47">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>14</v>
       </c>
@@ -10770,24 +13631,30 @@
         <v>1285</v>
       </c>
       <c r="H48">
-        <v>2308</v>
+        <v>702</v>
       </c>
       <c r="I48">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A52" s="13" t="s">
+        <v>886</v>
+      </c>
+      <c r="J48">
+        <v>803</v>
+      </c>
+      <c r="K48">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A52" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-    </row>
-    <row r="53" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="B52" s="15"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="15"/>
+      <c r="E52" s="15"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15"/>
+    </row>
+    <row r="53" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="1" t="s">
         <v>6</v>
@@ -10811,10 +13678,16 @@
         <v>24</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="J53" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="K53" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="7">
         <v>0.15</v>
       </c>
@@ -10851,7 +13724,7 @@
         <v>1344.8</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="8">
         <v>0.35</v>
       </c>
@@ -10888,7 +13761,7 @@
         <v>1748.2</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="8">
         <v>0.55000000000000004</v>
       </c>
@@ -10925,7 +13798,7 @@
         <v>1281.2</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="8">
         <v>0.7</v>
       </c>
@@ -10955,14 +13828,22 @@
       </c>
       <c r="H57">
         <f>AVERAGE(H44:H48)</f>
-        <v>2006.6</v>
+        <v>825.4</v>
       </c>
       <c r="I57">
         <f>AVERAGE(I44:I48)</f>
-        <v>1117.5999999999999</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+        <v>808.6</v>
+      </c>
+      <c r="J57">
+        <f>AVERAGE(J44:J48)</f>
+        <v>780.6</v>
+      </c>
+      <c r="K57">
+        <f>AVERAGE(K44:K48)</f>
+        <v>698.4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="I64" s="3"/>
       <c r="J64" s="1" t="s">
         <v>1</v>
@@ -10971,94 +13852,266 @@
         <v>0</v>
       </c>
       <c r="L64" s="10" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="M64" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="65" spans="9:13" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="N64" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="O64" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="9:15" x14ac:dyDescent="0.25">
       <c r="I65" s="7">
         <v>0.15</v>
       </c>
-      <c r="J65" s="20">
+      <c r="J65" s="13">
         <f>(G54 - F54) / G54</f>
         <v>0.4186260949746427</v>
       </c>
-      <c r="K65" s="20">
+      <c r="K65" s="13">
         <f>(G54 - G54) / G54</f>
         <v>0</v>
       </c>
-      <c r="L65" s="20">
+      <c r="L65" s="13">
         <f>(G54 - H54) / G54</f>
         <v>-1.0444137083141229</v>
       </c>
-      <c r="M65" s="20">
+      <c r="M65" s="13">
         <f>(G54 - I54) / G54</f>
         <v>-3.3348701398493823E-2</v>
       </c>
     </row>
-    <row r="66" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="66" spans="9:15" x14ac:dyDescent="0.25">
       <c r="I66" s="8">
         <v>0.35</v>
       </c>
-      <c r="J66" s="20">
-        <f t="shared" ref="J66:J68" si="4">(G55 - F55) / G55</f>
+      <c r="J66" s="13">
+        <f t="shared" ref="J66:J67" si="4">(G55 - F55) / G55</f>
         <v>0.43337943752881519</v>
       </c>
-      <c r="K66" s="20">
+      <c r="K66" s="13">
         <f t="shared" ref="K66:K68" si="5">(G55 - G55) / G55</f>
         <v>0</v>
       </c>
-      <c r="L66" s="20">
-        <f t="shared" ref="L66:L68" si="6">(G55 - H55) / G55</f>
+      <c r="L66" s="13">
+        <f t="shared" ref="L66:L67" si="6">(G55 - H55) / G55</f>
         <v>-0.56277854618103562</v>
       </c>
-      <c r="M66" s="20">
+      <c r="M66" s="13">
         <f t="shared" ref="M66:M68" si="7">(G55 - I55) / G55</f>
         <v>-0.34332257568772084</v>
       </c>
     </row>
-    <row r="67" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="67" spans="9:15" x14ac:dyDescent="0.25">
       <c r="I67" s="8">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J67" s="20">
+      <c r="J67" s="13">
         <f t="shared" si="4"/>
         <v>0.4021822652528047</v>
       </c>
-      <c r="K67" s="20">
+      <c r="K67" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L67" s="20">
+      <c r="L67" s="13">
         <f t="shared" si="6"/>
         <v>-0.74304595051483013</v>
       </c>
-      <c r="M67" s="20">
+      <c r="M67" s="13">
         <f t="shared" si="7"/>
         <v>1.5521745812202278E-2</v>
       </c>
     </row>
-    <row r="68" spans="9:13" x14ac:dyDescent="0.25">
+    <row r="68" spans="9:15" x14ac:dyDescent="0.25">
       <c r="I68" s="8">
         <v>0.7</v>
       </c>
-      <c r="J68" s="20">
-        <f t="shared" si="4"/>
+      <c r="J68" s="13">
+        <f>(G57 - F57) / G57</f>
         <v>0.41509143998770553</v>
       </c>
-      <c r="K68" s="20">
+      <c r="K68" s="13">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L68" s="20">
-        <f t="shared" si="6"/>
-        <v>-0.54187797756262468</v>
-      </c>
-      <c r="M68" s="20">
+      <c r="L68" s="13">
+        <f>(G57 - H57) / G57</f>
+        <v>0.36575995082219154</v>
+      </c>
+      <c r="M68" s="13">
         <f t="shared" si="7"/>
-        <v>0.14123251882587995</v>
+        <v>0.37866912555709237</v>
+      </c>
+      <c r="N68" s="13">
+        <f>(G57 - J57) / G57</f>
+        <v>0.40018441678192718</v>
+      </c>
+      <c r="O68" s="13">
+        <f>(G57 - K57) / G57</f>
+        <v>0.46334716459197794</v>
+      </c>
+    </row>
+    <row r="103" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D103" t="s">
+        <v>36</v>
+      </c>
+      <c r="F103" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C104" s="22"/>
+      <c r="D104" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F104" s="22"/>
+      <c r="G104" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="105" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C105" s="10">
+        <v>0</v>
+      </c>
+      <c r="D105" s="22">
+        <v>917</v>
+      </c>
+      <c r="F105" s="10">
+        <v>0</v>
+      </c>
+      <c r="G105" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C106" s="10">
+        <v>191</v>
+      </c>
+      <c r="D106" s="22">
+        <v>873</v>
+      </c>
+      <c r="F106" s="10">
+        <v>191</v>
+      </c>
+      <c r="G106" s="2">
+        <v>3.5799999999999998E-2</v>
+      </c>
+    </row>
+    <row r="107" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C107" s="10">
+        <v>382</v>
+      </c>
+      <c r="D107" s="23">
+        <v>812</v>
+      </c>
+      <c r="F107" s="10">
+        <v>382</v>
+      </c>
+      <c r="G107" s="2">
+        <v>7.15355805243445E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C108" s="10">
+        <v>573</v>
+      </c>
+      <c r="D108" s="23">
+        <v>736</v>
+      </c>
+      <c r="F108" s="10">
+        <v>573</v>
+      </c>
+      <c r="G108" s="2">
+        <v>0.12191011235955</v>
+      </c>
+    </row>
+    <row r="109" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C109" s="10">
+        <v>764</v>
+      </c>
+      <c r="D109" s="22">
+        <v>697</v>
+      </c>
+      <c r="F109" s="10">
+        <v>764</v>
+      </c>
+      <c r="G109" s="2">
+        <v>0.143071161048689</v>
+      </c>
+    </row>
+    <row r="110" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C110" s="24">
+        <v>955</v>
+      </c>
+      <c r="D110" s="22">
+        <v>731</v>
+      </c>
+      <c r="F110" s="24">
+        <v>955</v>
+      </c>
+      <c r="G110" s="2">
+        <v>0.21142322097378199</v>
+      </c>
+    </row>
+    <row r="111" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C111" s="24">
+        <v>1146</v>
+      </c>
+      <c r="D111" s="22">
+        <v>766</v>
+      </c>
+      <c r="F111" s="24">
+        <v>1146</v>
+      </c>
+      <c r="G111" s="2">
+        <v>0.42621722846441901</v>
+      </c>
+    </row>
+    <row r="112" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C112" s="24">
+        <v>1337</v>
+      </c>
+      <c r="D112" s="22">
+        <v>1090</v>
+      </c>
+      <c r="F112" s="24">
+        <v>1337</v>
+      </c>
+      <c r="G112" s="2">
+        <v>0.38876404494382</v>
+      </c>
+    </row>
+    <row r="113" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C113" s="25">
+        <v>1528</v>
+      </c>
+      <c r="D113" s="22">
+        <v>1152</v>
+      </c>
+      <c r="F113" s="25">
+        <v>1528</v>
+      </c>
+      <c r="G113" s="2">
+        <v>0.41217228464419398</v>
+      </c>
+    </row>
+    <row r="114" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C114" s="25">
+        <v>1719</v>
+      </c>
+      <c r="D114" s="22">
+        <v>1428</v>
+      </c>
+      <c r="F114" s="25">
+        <v>1719</v>
+      </c>
+      <c r="G114" s="2">
+        <v>0.45850000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -11092,26 +14145,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -11286,26 +14339,26 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -11480,26 +14533,26 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
@@ -11674,26 +14727,26 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+      <c r="A35" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="18"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="18"/>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
@@ -11745,7 +14798,7 @@
         <v>0.82399999999999995</v>
       </c>
       <c r="H38">
-        <v>3.2570000000000001</v>
+        <v>3.4750000000000001</v>
       </c>
       <c r="I38">
         <v>1.825</v>
@@ -11774,7 +14827,7 @@
         <v>0.80400000000000005</v>
       </c>
       <c r="H39">
-        <v>3.5379999999999998</v>
+        <v>3.5790000000000002</v>
       </c>
       <c r="I39">
         <v>1.714</v>
@@ -11803,7 +14856,7 @@
         <v>0.77900000000000003</v>
       </c>
       <c r="H40">
-        <v>3.0139999999999998</v>
+        <v>3.3420000000000001</v>
       </c>
       <c r="I40">
         <v>1.984</v>
@@ -11832,7 +14885,7 @@
         <v>0.86699999999999999</v>
       </c>
       <c r="H41">
-        <v>3.069</v>
+        <v>3.69</v>
       </c>
       <c r="I41">
         <v>1.8380000000000001</v>
@@ -11861,22 +14914,22 @@
         <v>0.77500000000000002</v>
       </c>
       <c r="H42">
-        <v>3.2890000000000001</v>
+        <v>3.24</v>
       </c>
       <c r="I42">
         <v>1.859</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
     </row>
     <row r="50" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
@@ -12046,7 +15099,7 @@
       </c>
       <c r="H54">
         <f>AVERAGE(H38:H42)</f>
-        <v>3.2334000000000005</v>
+        <v>3.4652000000000003</v>
       </c>
       <c r="I54">
         <f>AVERAGE(I38:I42)</f>
@@ -12085,26 +15138,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="15"/>
-      <c r="F2" s="15"/>
-      <c r="G2" s="15"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -12252,11 +15305,11 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -12358,26 +15411,26 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+      <c r="A21" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
+      <c r="B22" s="17"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
     </row>
     <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
@@ -12522,11 +15575,11 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
@@ -12628,26 +15681,26 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+      <c r="A40" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="16"/>
+      <c r="F40" s="16"/>
+      <c r="G40" s="16"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
     </row>
     <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
@@ -12792,11 +15845,11 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
+      <c r="A49" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
@@ -12898,26 +15951,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
+      <c r="A59" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="16"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="16"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="15" t="s">
+      <c r="A60" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="15"/>
-      <c r="C60" s="15"/>
-      <c r="D60" s="15"/>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
-      <c r="G60" s="15"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="17"/>
+      <c r="D60" s="17"/>
+      <c r="E60" s="17"/>
+      <c r="F60" s="17"/>
+      <c r="G60" s="17"/>
     </row>
     <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
@@ -13032,11 +16085,11 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="19" t="s">
+      <c r="A68" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="19"/>
-      <c r="C68" s="19"/>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
@@ -13138,26 +16191,26 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="13" t="s">
+      <c r="A78" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
+      <c r="B78" s="15"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="15"/>
+      <c r="E78" s="15"/>
+      <c r="F78" s="15"/>
+      <c r="G78" s="15"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="s">
+      <c r="A79" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="B79" s="15"/>
-      <c r="C79" s="15"/>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
-      <c r="G79" s="15"/>
+      <c r="B79" s="17"/>
+      <c r="C79" s="17"/>
+      <c r="D79" s="17"/>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
@@ -13167,7 +16220,7 @@
       <c r="C80" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D80" s="21" t="s">
+      <c r="D80" s="14" t="s">
         <v>27</v>
       </c>
       <c r="E80" s="11" t="s">
@@ -13178,19 +16231,19 @@
       <c r="A81" s="7">
         <v>0.15</v>
       </c>
-      <c r="B81" s="20">
+      <c r="B81" s="13">
         <f>AVERAGE(F4:F8)</f>
         <v>0.27960000000000002</v>
       </c>
-      <c r="C81" s="20">
+      <c r="C81" s="13">
         <f>AVERAGE(G4:G8)</f>
         <v>0.27698</v>
       </c>
-      <c r="D81" s="20">
+      <c r="D81" s="13">
         <f>AVERAGE(H4:H8)</f>
         <v>0</v>
       </c>
-      <c r="E81" s="20">
+      <c r="E81" s="13">
         <f>AVERAGE(I4:I8)</f>
         <v>4.9445999999999997E-2</v>
       </c>
@@ -13199,19 +16252,19 @@
       <c r="A82" s="8">
         <v>0.35</v>
       </c>
-      <c r="B82" s="20">
+      <c r="B82" s="13">
         <f>AVERAGE(F24:F28)</f>
         <v>0.27060000000000006</v>
       </c>
-      <c r="C82" s="20">
+      <c r="C82" s="13">
         <f>AVERAGE(G24:G28)</f>
         <v>0.27698</v>
       </c>
-      <c r="D82" s="20">
+      <c r="D82" s="13">
         <f>AVERAGE(H24:H28)</f>
         <v>0</v>
       </c>
-      <c r="E82" s="20">
+      <c r="E82" s="13">
         <f>AVERAGE(I24:I28)</f>
         <v>3.5687999999999998E-2</v>
       </c>
@@ -13220,19 +16273,19 @@
       <c r="A83" s="8">
         <v>0.55000000000000004</v>
       </c>
-      <c r="B83" s="20">
+      <c r="B83" s="13">
         <f>AVERAGE(F43:F47)</f>
         <v>0.26160000000000005</v>
       </c>
-      <c r="C83" s="20">
+      <c r="C83" s="13">
         <f>AVERAGE(G43:G47)</f>
         <v>0.27698</v>
       </c>
-      <c r="D83" s="20">
+      <c r="D83" s="13">
         <f>AVERAGE(H43:H47)</f>
         <v>0</v>
       </c>
-      <c r="E83" s="20">
+      <c r="E83" s="13">
         <f>AVERAGE(I43:I47)</f>
         <v>4.1377999999999998E-2</v>
       </c>
@@ -13241,29 +16294,29 @@
       <c r="A84" s="8">
         <v>0.7</v>
       </c>
-      <c r="B84" s="20">
+      <c r="B84" s="13">
         <f>AVERAGE(F62:F66)</f>
         <v>0.26463999999999999</v>
       </c>
-      <c r="C84" s="20">
+      <c r="C84" s="13">
         <f>AVERAGE(G62:G66)</f>
         <v>0.27698</v>
       </c>
-      <c r="D84" s="20">
+      <c r="D84" s="13">
         <f>AVERAGE(H62:H66)</f>
         <v>0</v>
       </c>
-      <c r="E84" s="20">
+      <c r="E84" s="13">
         <f>AVERAGE(I62:I66)</f>
         <v>4.4226000000000001E-2</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="19" t="s">
+      <c r="A90" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="B90" s="19"/>
-      <c r="C90" s="19"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="21"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
@@ -13361,21 +16414,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A41:G41"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13398,26 +16451,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -13592,26 +16645,26 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
+      <c r="A13" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="16"/>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16"/>
-      <c r="G14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="20"/>
     </row>
     <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -13786,26 +16839,26 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+      <c r="A24" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="18"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
@@ -13980,26 +17033,26 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+      <c r="A36" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
+      <c r="A37" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="20"/>
     </row>
     <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
@@ -14051,7 +17104,7 @@
         <v>4</v>
       </c>
       <c r="H39">
-        <v>708</v>
+        <v>130</v>
       </c>
       <c r="I39">
         <v>327</v>
@@ -14080,7 +17133,7 @@
         <v>9</v>
       </c>
       <c r="H40">
-        <v>1031</v>
+        <v>134</v>
       </c>
       <c r="I40">
         <v>258</v>
@@ -14109,7 +17162,7 @@
         <v>17</v>
       </c>
       <c r="H41">
-        <v>782</v>
+        <v>142</v>
       </c>
       <c r="I41">
         <v>577</v>
@@ -14138,7 +17191,7 @@
         <v>5</v>
       </c>
       <c r="H42">
-        <v>679</v>
+        <v>124</v>
       </c>
       <c r="I42">
         <v>326</v>
@@ -14167,33 +17220,33 @@
         <v>10</v>
       </c>
       <c r="H43">
-        <v>962</v>
+        <v>119</v>
       </c>
       <c r="I43">
         <v>356</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="13"/>
+      <c r="B59" s="15"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="15"/>
+      <c r="E59" s="15"/>
+      <c r="F59" s="15"/>
+      <c r="G59" s="15"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="F60" s="16"/>
-      <c r="G60" s="18"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="18"/>
+      <c r="E60" s="18"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="20"/>
     </row>
     <row r="61" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
@@ -14363,7 +17416,7 @@
       </c>
       <c r="H65">
         <f>AVERAGE(H39:H43)</f>
-        <v>832.4</v>
+        <v>129.80000000000001</v>
       </c>
       <c r="I65">
         <f>AVERAGE(I39:I43)</f>

--- a/Experiments data/Contraction Limit/Contraction_Limit_PGP_Graph.xlsx
+++ b/Experiments data/Contraction Limit/Contraction_Limit_PGP_Graph.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fengw\OneDrive\Documents\GitHub\KaMinPar_Java\Experiments data\Contraction Limit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED8CB9B-757D-4700-9CD7-8B7B2CEE9B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC26555-89B1-4CA6-9E45-270F1F75831D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Edge Cuts" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="CCM" sheetId="5" r:id="rId3"/>
     <sheet name="Contiguity" sheetId="7" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -354,6 +351,16 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -374,16 +381,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12400,114 +12397,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Edge Cuts"/>
-      <sheetName val="Runtimes"/>
-      <sheetName val="CCM"/>
-      <sheetName val="Contiguity"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="102">
-          <cell r="B102" t="str">
-            <v>Deep NUGP</v>
-          </cell>
-        </row>
-        <row r="103">
-          <cell r="A103">
-            <v>0</v>
-          </cell>
-          <cell r="B103">
-            <v>1318</v>
-          </cell>
-        </row>
-        <row r="104">
-          <cell r="A104">
-            <v>20</v>
-          </cell>
-          <cell r="B104">
-            <v>1319</v>
-          </cell>
-        </row>
-        <row r="105">
-          <cell r="A105">
-            <v>40</v>
-          </cell>
-          <cell r="B105">
-            <v>1307</v>
-          </cell>
-        </row>
-        <row r="106">
-          <cell r="A106">
-            <v>60</v>
-          </cell>
-          <cell r="B106">
-            <v>1258</v>
-          </cell>
-        </row>
-        <row r="107">
-          <cell r="A107">
-            <v>80</v>
-          </cell>
-          <cell r="B107">
-            <v>1159</v>
-          </cell>
-        </row>
-        <row r="108">
-          <cell r="A108">
-            <v>100</v>
-          </cell>
-          <cell r="B108">
-            <v>1149</v>
-          </cell>
-        </row>
-        <row r="109">
-          <cell r="A109">
-            <v>120</v>
-          </cell>
-          <cell r="B109">
-            <v>1234</v>
-          </cell>
-        </row>
-        <row r="110">
-          <cell r="A110">
-            <v>140</v>
-          </cell>
-          <cell r="B110">
-            <v>1341</v>
-          </cell>
-        </row>
-        <row r="111">
-          <cell r="A111">
-            <v>160</v>
-          </cell>
-          <cell r="B111">
-            <v>1416</v>
-          </cell>
-        </row>
-        <row r="112">
-          <cell r="A112">
-            <v>180</v>
-          </cell>
-          <cell r="B112">
-            <v>1659</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -12817,26 +12706,26 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
@@ -13016,26 +12905,26 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="16"/>
-      <c r="G15" s="16"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="22"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
     </row>
     <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
@@ -13215,26 +13104,26 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
     </row>
     <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
@@ -13414,26 +13303,26 @@
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
+      <c r="A41" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
+      <c r="A42" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="21"/>
+      <c r="G42" s="21"/>
     </row>
     <row r="43" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
@@ -13644,15 +13533,15 @@
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" s="15" t="s">
+      <c r="A52" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
     </row>
     <row r="53" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
@@ -13965,11 +13854,11 @@
       </c>
     </row>
     <row r="104" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C104" s="22"/>
+      <c r="C104" s="15"/>
       <c r="D104" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="F104" s="22"/>
+      <c r="F104" s="15"/>
       <c r="G104" s="11" t="s">
         <v>37</v>
       </c>
@@ -13978,7 +13867,7 @@
       <c r="C105" s="10">
         <v>0</v>
       </c>
-      <c r="D105" s="22">
+      <c r="D105" s="15">
         <v>917</v>
       </c>
       <c r="F105" s="10">
@@ -13992,7 +13881,7 @@
       <c r="C106" s="10">
         <v>191</v>
       </c>
-      <c r="D106" s="22">
+      <c r="D106" s="15">
         <v>873</v>
       </c>
       <c r="F106" s="10">
@@ -14006,7 +13895,7 @@
       <c r="C107" s="10">
         <v>382</v>
       </c>
-      <c r="D107" s="23">
+      <c r="D107" s="16">
         <v>812</v>
       </c>
       <c r="F107" s="10">
@@ -14020,7 +13909,7 @@
       <c r="C108" s="10">
         <v>573</v>
       </c>
-      <c r="D108" s="23">
+      <c r="D108" s="16">
         <v>736</v>
       </c>
       <c r="F108" s="10">
@@ -14034,7 +13923,7 @@
       <c r="C109" s="10">
         <v>764</v>
       </c>
-      <c r="D109" s="22">
+      <c r="D109" s="15">
         <v>697</v>
       </c>
       <c r="F109" s="10">
@@ -14045,13 +13934,13 @@
       </c>
     </row>
     <row r="110" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C110" s="24">
+      <c r="C110" s="17">
         <v>955</v>
       </c>
-      <c r="D110" s="22">
+      <c r="D110" s="15">
         <v>731</v>
       </c>
-      <c r="F110" s="24">
+      <c r="F110" s="17">
         <v>955</v>
       </c>
       <c r="G110" s="2">
@@ -14059,13 +13948,13 @@
       </c>
     </row>
     <row r="111" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C111" s="24">
+      <c r="C111" s="17">
         <v>1146</v>
       </c>
-      <c r="D111" s="22">
+      <c r="D111" s="15">
         <v>766</v>
       </c>
-      <c r="F111" s="24">
+      <c r="F111" s="17">
         <v>1146</v>
       </c>
       <c r="G111" s="2">
@@ -14073,13 +13962,13 @@
       </c>
     </row>
     <row r="112" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C112" s="24">
+      <c r="C112" s="17">
         <v>1337</v>
       </c>
-      <c r="D112" s="22">
+      <c r="D112" s="15">
         <v>1090</v>
       </c>
-      <c r="F112" s="24">
+      <c r="F112" s="17">
         <v>1337</v>
       </c>
       <c r="G112" s="2">
@@ -14087,13 +13976,13 @@
       </c>
     </row>
     <row r="113" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C113" s="25">
+      <c r="C113" s="18">
         <v>1528</v>
       </c>
-      <c r="D113" s="22">
+      <c r="D113" s="15">
         <v>1152</v>
       </c>
-      <c r="F113" s="25">
+      <c r="F113" s="18">
         <v>1528</v>
       </c>
       <c r="G113" s="2">
@@ -14101,13 +13990,13 @@
       </c>
     </row>
     <row r="114" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C114" s="25">
+      <c r="C114" s="18">
         <v>1719</v>
       </c>
-      <c r="D114" s="22">
+      <c r="D114" s="15">
         <v>1428</v>
       </c>
-      <c r="F114" s="25">
+      <c r="F114" s="18">
         <v>1719</v>
       </c>
       <c r="G114" s="2">
@@ -14145,26 +14034,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -14339,26 +14228,26 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="20"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="24"/>
     </row>
     <row r="15" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -14533,26 +14422,26 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="24"/>
     </row>
     <row r="26" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
@@ -14727,26 +14616,26 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
+      <c r="A36" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="18"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="20"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="22"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="24"/>
     </row>
     <row r="37" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
@@ -14921,15 +14810,15 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
     </row>
     <row r="50" spans="1:9" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
@@ -15138,26 +15027,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
@@ -15305,11 +15194,11 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -15411,26 +15300,26 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
     </row>
     <row r="23" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
@@ -15575,11 +15464,11 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="21"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
@@ -15681,26 +15570,26 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
+      <c r="A40" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21"/>
+      <c r="G41" s="21"/>
     </row>
     <row r="42" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
@@ -15845,11 +15734,11 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B49" s="21"/>
-      <c r="C49" s="21"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
@@ -15951,26 +15840,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
+      <c r="A59" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="16"/>
-      <c r="G59" s="16"/>
+      <c r="B59" s="20"/>
+      <c r="C59" s="20"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
+      <c r="A60" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B60" s="17"/>
-      <c r="C60" s="17"/>
-      <c r="D60" s="17"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="17"/>
-      <c r="G60" s="17"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
     </row>
     <row r="61" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
@@ -16085,11 +15974,11 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="21" t="s">
+      <c r="A68" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
@@ -16191,26 +16080,26 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="15" t="s">
+      <c r="A78" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B78" s="15"/>
-      <c r="C78" s="15"/>
-      <c r="D78" s="15"/>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
-      <c r="G78" s="15"/>
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="19"/>
+      <c r="F78" s="19"/>
+      <c r="G78" s="19"/>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="17" t="s">
+      <c r="A79" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B79" s="17"/>
-      <c r="C79" s="17"/>
-      <c r="D79" s="17"/>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17"/>
+      <c r="B79" s="21"/>
+      <c r="C79" s="21"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="21"/>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
@@ -16312,11 +16201,11 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="21" t="s">
+      <c r="A90" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B90" s="21"/>
-      <c r="C90" s="21"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="25"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
@@ -16414,21 +16303,21 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A79:G79"/>
+    <mergeCell ref="A90:C90"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A21:G21"/>
     <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A78:G78"/>
-    <mergeCell ref="A79:G79"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A60:G60"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A59:G59"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16451,26 +16340,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="20"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="24"/>
     </row>
     <row r="3" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
@@ -16645,26 +16534,26 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="20"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="24"/>
     </row>
     <row r="15" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
@@ -16839,26 +16728,26 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="18"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="20"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="24"/>
     </row>
     <row r="26" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
@@ -17033,26 +16922,26 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="18"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18"/>
-      <c r="G37" s="20"/>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="24"/>
     </row>
     <row r="38" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
@@ -17227,26 +17116,26 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="15" t="s">
+      <c r="A59" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="15"/>
-      <c r="C59" s="15"/>
-      <c r="D59" s="15"/>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
-      <c r="G59" s="15"/>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="19" t="s">
+      <c r="A60" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B60" s="18"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="18"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="20"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="24"/>
     </row>
     <row r="61" spans="1:9" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
